--- a/docs/wind-mcp-行情工具验证-20260721.xlsx
+++ b/docs/wind-mcp-行情工具验证-20260721.xlsx
@@ -10,13 +10,16 @@
     <sheet sheetId="4" name="出参结构" state="visible" r:id="rId7"/>
     <sheet sheetId="5" name="实测记录" state="visible" r:id="rId8"/>
     <sheet sheetId="6" name="易错点" state="visible" r:id="rId9"/>
+    <sheet sheetId="7" name="日期与时间语义" state="visible" r:id="rId10"/>
+    <sheet sheetId="8" name="复测记录-第二轮" state="visible" r:id="rId11"/>
+    <sheet sheetId="9" name="稳定性重复测试" state="visible" r:id="rId12"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="759" uniqueCount="357">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1124" uniqueCount="521">
   <si>
     <t>项</t>
   </si>
@@ -102,6 +105,30 @@
     <t>因此「省略 begin/end 即返回最新交易日」这一行为仅对生产线成立；开发线要求显式传日期。跨线复用参数前请先确认所用 skill 版本。</t>
   </si>
   <si>
+    <t>—— 第二轮复测 ——</t>
+  </si>
+  <si>
+    <t>2026-07-21 当日晚些时候针对 quote 三工具做了日期兼容专项复测，共 27 条矩阵用例 + 46 次重复稳定性调用</t>
+  </si>
+  <si>
+    <t>★结论变更</t>
+  </si>
+  <si>
+    <t>LAST 在第一轮为必失败（3 个 server 全挂、对照组穿插通过），第二轮复测 10/10 成功、交替对照 14/15 成功。两轮之间后端行为发生了变更，第一轮的 LAST 结论已作废。</t>
+  </si>
+  <si>
+    <t>★未变更结论</t>
+  </si>
+  <si>
+    <t>错误码重载问题依然成立且证据更强：解析不了的日期值（XYZZY / 2026721 / abc）确定性返回 TEMPORARILY_UNAVAILABLE 3/3。</t>
+  </si>
+  <si>
+    <t>★新增风险</t>
+  </si>
+  <si>
+    <t>分钟行情长区间会撑爆上下文：20260101~20260721 返回 31335 行 / 4.1 MB / 约 108 万 token，无行数上限也无分页提示。</t>
+  </si>
+  <si>
     <t>#</t>
   </si>
   <si>
@@ -948,19 +975,19 @@
     <t>必须逐次比对返回的「Wind代码」列与请求的 windcode；不一致即丢弃。不可依赖是否报错来判断</t>
   </si>
   <si>
-    <t>quote 传 LAST 被伪装成服务故障</t>
+    <t>LAST 支持状态在同一天内发生过变更，行为不稳定</t>
   </si>
   <si>
     <t>quote(3)</t>
   </si>
   <si>
-    <t>begin/end="LAST" → TEMPORARILY_UNAVAILABLE「服务暂时不可用，请稍后重试」，3/3 必现；垃圾值 XYZZY 同码</t>
-  </si>
-  <si>
-    <t>参数错误被报成后端故障，处置建议是「原样重试/稍后再试」，调用方永远不会去修参数</t>
-  </si>
-  <si>
-    <t>取最新数据请直接省略 begin/end。绝不可传 LAST</t>
+    <t>第一轮：begin/end="LAST" 在 stock/fund/index 三个 server 全部失败（对照组穿插通过）。第二轮同日复测：10/10 成功，交替对照 14/15 成功（yyyyMMdd 对照 15/15），小写 last、带空格 " LAST " 亦可用</t>
+  </si>
+  <si>
+    <t>同一入参在同一天内由“必失败”变为“基本可用”，且无版本公告。调用方无法判断当前后端是否支持，按任一轮结论写死都会在另一时段出错</t>
+  </si>
+  <si>
+    <t>不要依赖 LAST。取最新交易日请直接省略 begin/end——该写法两轮均稳定可用，且语义无歧义</t>
   </si>
   <si>
     <t>未来日期被静默忽略，返回最新交易日数据</t>
@@ -1023,16 +1050,16 @@
     <t>仍按文档只传 references/indicators.md 内的精确中文字段；以返回的列名为准核对</t>
   </si>
   <si>
-    <t>起止日期颠倒返回空结果而非报错</t>
-  </si>
-  <si>
-    <t>begin_date=20260721 &gt; end_date=20260601 → rows=0，status 成功，无任何错误</t>
-  </si>
-  <si>
-    <t>空结果与「该区间确实无数据」无法区分，掩盖参数写反的 bug</t>
-  </si>
-  <si>
-    <t>调用前断言 begin_date &lt;= end_date</t>
+    <t>起止日期颠倒时 quote 与 kline 行为相反，且都不报错</t>
+  </si>
+  <si>
+    <t>begin&gt;end 时：quote 自动纠正并返回完整区间（20260721&gt;20260717 → 720 行，自 0717 起）；kline 则返回 rows=0</t>
+  </si>
+  <si>
+    <t>同一套行情工具两种容错策略，都不报错。空结果与「确实无数据」无法区分，自动纠正则掩盖参数写反</t>
+  </si>
+  <si>
+    <t>调用前自行断言 begin &lt;= end，不要依赖任一方的容错</t>
   </si>
   <si>
     <t>跨类调用不被拦截</t>
@@ -1087,6 +1114,474 @@
   </si>
   <si>
     <t>解析时对 windcode / indicator_units 做存在性判断</t>
+  </si>
+  <si>
+    <t>长区间分钟行情会撑爆上下文，无上限无分页</t>
+  </si>
+  <si>
+    <t>20260101~20260721（约半年）返回 31335 行 / 4339297 字节 / 4.1 MB / 约 108 万 token，正常返回无任何告警</t>
+  </si>
+  <si>
+    <t>半年区间是很自然的用户请求，一次调用即可打爆任意 Agent 的上下文窗口，且事前无从预估</t>
+  </si>
+  <si>
+    <t>分钟行情严格限制在数个交易日内（1 交易日=240 行）。需要长区间请改用 kline 日线</t>
+  </si>
+  <si>
+    <t>TEMPORARILY_UNAVAILABLE 同时表示参数错误和瞬时故障</t>
+  </si>
+  <si>
+    <t>解析不了的日期值确定性返回该码：XYZZY 3/3、2026721（无补零）3/3、abc 3/3；同时真正的瞬时抖动也返回该码（有效入参偶发 1/15）</t>
+  </si>
+  <si>
+    <t>一个错误码承担两种互斥语义。其提示为「请稍后重试」，而重试永远救不回参数错误，导致参数问题被长期误判为服务不稳定</t>
+  </si>
+  <si>
+    <t>收到该码时先自查日期格式是否为 8 位补零，不要盲目重试；建议推动后端拆分错误码</t>
+  </si>
+  <si>
+    <t>日期分隔符宽松但必须 8 位补零</t>
+  </si>
+  <si>
+    <t>20260721 / 2026-07-21 / 2026/07/21 / 2026.07.21 均可；但 2026721（无补零）失败，"" 空串失败，"20260721 09:30" 带时间失败</t>
+  </si>
+  <si>
+    <t>文档只写 yyyyMMdd（合法子集，不会出错），但易误以为可传任意日期串</t>
+  </si>
+  <si>
+    <t>统一使用 yyyyMMdd 8 位补零；不要传空串或带时间的值</t>
+  </si>
+  <si>
+    <t>分类</t>
+  </si>
+  <si>
+    <t>写法 / 场景</t>
+  </si>
+  <si>
+    <t>实测结果</t>
+  </si>
+  <si>
+    <t>格式-可用</t>
+  </si>
+  <si>
+    <t>省略 begin 与 end</t>
+  </si>
+  <si>
+    <t>✅ 当日 240 行</t>
+  </si>
+  <si>
+    <t>两轮均稳定可用，语义无歧义，推荐写法</t>
+  </si>
+  <si>
+    <t>20260721（yyyyMMdd）</t>
+  </si>
+  <si>
+    <t>✅ 240 行</t>
+  </si>
+  <si>
+    <t>文档写法，推荐</t>
+  </si>
+  <si>
+    <t>2026-07-21（ISO）</t>
+  </si>
+  <si>
+    <t>后端接受，但生产文档未记载</t>
+  </si>
+  <si>
+    <t>2026/07/21（斜杠）</t>
+  </si>
+  <si>
+    <t>后端接受，不建议依赖</t>
+  </si>
+  <si>
+    <t>2026.07.21（点号）</t>
+  </si>
+  <si>
+    <t>LAST / last / " LAST "</t>
+  </si>
+  <si>
+    <t>✅ 240 行（第二轮）</t>
+  </si>
+  <si>
+    <t>★ 第一轮为必失败，同日第二轮可用；后端做了 trim 与大小写归一。行为不稳定，勿依赖</t>
+  </si>
+  <si>
+    <t>只传 begin 或只传 end</t>
+  </si>
+  <si>
+    <t>另一端由后端自动补齐</t>
+  </si>
+  <si>
+    <t>格式-失败</t>
+  </si>
+  <si>
+    <t>"" 空字符串</t>
+  </si>
+  <si>
+    <t>❌ UNKNOWN</t>
+  </si>
+  <si>
+    <t>2026721（无补零）</t>
+  </si>
+  <si>
+    <t>❌ TEMPORARILY_UNAVAILABLE 3/3</t>
+  </si>
+  <si>
+    <t>确定性失败，但被报成服务故障</t>
+  </si>
+  <si>
+    <t>20260721 09:30（带时间）</t>
+  </si>
+  <si>
+    <t>❌ TOOL_RUNTIME_ERROR</t>
+  </si>
+  <si>
+    <t>begin/end 只接受日期，不接受时刻</t>
+  </si>
+  <si>
+    <t>20261332（13 月）</t>
+  </si>
+  <si>
+    <t>❌ TOOL_RUNTIME_ERROR 3/3</t>
+  </si>
+  <si>
+    <t>非法日期与不可解析串走不同错误码</t>
+  </si>
+  <si>
+    <t>时间-粒度</t>
+  </si>
+  <si>
+    <t>一个交易日的行数</t>
+  </si>
+  <si>
+    <t>240 行</t>
+  </si>
+  <si>
+    <t>1 分钟粒度；09:30:00 → 15:00:00</t>
+  </si>
+  <si>
+    <t>午休时段</t>
+  </si>
+  <si>
+    <t>无数据</t>
+  </si>
+  <si>
+    <t>11:30–13:00 为缺口，不补行</t>
+  </si>
+  <si>
+    <t>时间-时区</t>
+  </si>
+  <si>
+    <t>TIME 列格式</t>
+  </si>
+  <si>
+    <t>ISO8601 带 +08:00</t>
+  </si>
+  <si>
+    <t>如 2026-07-21T09:30:00.000+08:00</t>
+  </si>
+  <si>
+    <t>时间-区间</t>
+  </si>
+  <si>
+    <t>端点是否包含</t>
+  </si>
+  <si>
+    <t>含两端</t>
+  </si>
+  <si>
+    <t>0720~0721 = 480 行（2 个交易日）</t>
+  </si>
+  <si>
+    <t>跨周末 0717~0721</t>
+  </si>
+  <si>
+    <t>720 行</t>
+  </si>
+  <si>
+    <t>仅计 3 个交易日，周末不产生空行</t>
+  </si>
+  <si>
+    <t>周末单日 20260718</t>
+  </si>
+  <si>
+    <t>0 行，无报错</t>
+  </si>
+  <si>
+    <t>与「确实无数据」不可区分</t>
+  </si>
+  <si>
+    <t>begin &gt; end 颠倒</t>
+  </si>
+  <si>
+    <t>720 行（自动纠正）</t>
+  </si>
+  <si>
+    <t>★ 与 kline 相反：kline 同场景返回 0 行</t>
+  </si>
+  <si>
+    <t>时间-越界</t>
+  </si>
+  <si>
+    <t>未来日期 20301231</t>
+  </si>
+  <si>
+    <t>240 行，实为当日数据</t>
+  </si>
+  <si>
+    <t>★ 静默返回 2026-07-21 数据，无任何提示</t>
+  </si>
+  <si>
+    <t>远期历史 20200102</t>
+  </si>
+  <si>
+    <t>0 行</t>
+  </si>
+  <si>
+    <t>分钟行情有保留期，不覆盖远期</t>
+  </si>
+  <si>
+    <t>时间-体量</t>
+  </si>
+  <si>
+    <t>20260101~20260721（半年）</t>
+  </si>
+  <si>
+    <t>31335 行 / 4.1 MB / ~108 万 token</t>
+  </si>
+  <si>
+    <t>★ 无行数上限、无分页、无告警，足以打爆上下文</t>
+  </si>
+  <si>
+    <t>首行时间</t>
+  </si>
+  <si>
+    <t>末行时间</t>
+  </si>
+  <si>
+    <t>LAST</t>
+  </si>
+  <si>
+    <t>begin/end="LAST"</t>
+  </si>
+  <si>
+    <t>2026-07-21T09:30:00.000+08:00</t>
+  </si>
+  <si>
+    <t>2026-07-21T15:00:00.000+08:00</t>
+  </si>
+  <si>
+    <t>小写 "last"</t>
+  </si>
+  <si>
+    <t>{"windcode":"600519.SH","begin":"last","end":"last"}</t>
+  </si>
+  <si>
+    <t>带空格 " LAST "</t>
+  </si>
+  <si>
+    <t>{"windcode":"600519.SH","begin":" LAST ","end":" LAST "}</t>
+  </si>
+  <si>
+    <t>仅 begin=LAST</t>
+  </si>
+  <si>
+    <t>{"windcode":"600519.SH","begin":"LAST","end":"20260721"}</t>
+  </si>
+  <si>
+    <t>仅 end=LAST</t>
+  </si>
+  <si>
+    <t>{"windcode":"600519.SH","begin":"20260721","end":"LAST"}</t>
+  </si>
+  <si>
+    <t>格式</t>
+  </si>
+  <si>
+    <t>省略 begin/end</t>
+  </si>
+  <si>
+    <t>{"windcode":"600519.SH","begin":"20260721","end":"20260721"}</t>
+  </si>
+  <si>
+    <t>ISO yyyy-MM-dd</t>
+  </si>
+  <si>
+    <t>{"windcode":"600519.SH","begin":"2026-07-21","end":"2026-07-21"}</t>
+  </si>
+  <si>
+    <t>斜杠 yyyy/MM/dd</t>
+  </si>
+  <si>
+    <t>{"windcode":"600519.SH","begin":"2026/07/21","end":"2026/07/21"}</t>
+  </si>
+  <si>
+    <t>点号 yyyy.MM.dd</t>
+  </si>
+  <si>
+    <t>{"windcode":"600519.SH","begin":"2026.07.21","end":"2026.07.21"}</t>
+  </si>
+  <si>
+    <t>空字符串</t>
+  </si>
+  <si>
+    <t>{"windcode":"600519.SH","begin":"","end":""}</t>
+  </si>
+  <si>
+    <t>UNKNOWN</t>
+  </si>
+  <si>
+    <t>仅传 begin</t>
+  </si>
+  <si>
+    <t>{"windcode":"600519.SH","begin":"20260721"}</t>
+  </si>
+  <si>
+    <t>仅传 end</t>
+  </si>
+  <si>
+    <t>{"windcode":"600519.SH","end":"20260721"}</t>
+  </si>
+  <si>
+    <t>紧凑无补零 2026721</t>
+  </si>
+  <si>
+    <t>{"windcode":"600519.SH","begin":"2026721","end":"2026721"}</t>
+  </si>
+  <si>
+    <t>带时间 20260721 09:30</t>
+  </si>
+  <si>
+    <t>{"windcode":"600519.SH","begin":"20260721 09:30","end":"20260721 15:00"}</t>
+  </si>
+  <si>
+    <t>TOOL_RUNTIME_ERROR</t>
+  </si>
+  <si>
+    <t>时间</t>
+  </si>
+  <si>
+    <t>当日 20260721(周二)</t>
+  </si>
+  <si>
+    <t>周末 20260718(周六)</t>
+  </si>
+  <si>
+    <t>{"windcode":"600519.SH","begin":"20260718","end":"20260718"}</t>
+  </si>
+  <si>
+    <t>{"windcode":"600519.SH","begin":"20260717","end":"20260721"}</t>
+  </si>
+  <si>
+    <t>2026-07-17T09:30:00.000+08:00</t>
+  </si>
+  <si>
+    <t>两日区间 0720~0721</t>
+  </si>
+  <si>
+    <t>2026-07-20T09:30:00.000+08:00</t>
+  </si>
+  <si>
+    <t>begin&gt;end 颠倒</t>
+  </si>
+  <si>
+    <t>{"windcode":"600519.SH","begin":"20260721","end":"20260717"}</t>
+  </si>
+  <si>
+    <t>未来 20301231</t>
+  </si>
+  <si>
+    <t>{"windcode":"600519.SH","begin":"20200102","end":"20200102"}</t>
+  </si>
+  <si>
+    <t>超长区间 20260101~0721</t>
+  </si>
+  <si>
+    <t>{"windcode":"600519.SH","begin":"20260101","end":"20260721"}</t>
+  </si>
+  <si>
+    <t>2026-01-05T09:30:00.000+08:00</t>
+  </si>
+  <si>
+    <t>跨工具</t>
+  </si>
+  <si>
+    <t>fund LAST</t>
+  </si>
+  <si>
+    <t>{"windcode":"510300.SH","begin":"LAST","end":"LAST"}</t>
+  </si>
+  <si>
+    <t>fund ISO</t>
+  </si>
+  <si>
+    <t>{"windcode":"510300.SH","begin":"2026-07-21","end":"2026-07-21"}</t>
+  </si>
+  <si>
+    <t>index LAST</t>
+  </si>
+  <si>
+    <t>{"windcode":"000300.SH","begin":"LAST","end":"LAST"}</t>
+  </si>
+  <si>
+    <t>index ISO</t>
+  </si>
+  <si>
+    <t>{"windcode":"000300.SH","begin":"2026-07-21","end":"2026-07-21"}</t>
+  </si>
+  <si>
+    <t>重复次数</t>
+  </si>
+  <si>
+    <t>成功</t>
+  </si>
+  <si>
+    <t>失败</t>
+  </si>
+  <si>
+    <t>结论</t>
+  </si>
+  <si>
+    <t>begin/end = "LAST"（连续）</t>
+  </si>
+  <si>
+    <t>第二轮：稳定可用</t>
+  </si>
+  <si>
+    <t>begin/end = "LAST"（与 yyyyMMdd 交替对照）</t>
+  </si>
+  <si>
+    <t>1 次失败落在噪声范围，与对照组无显著差异</t>
+  </si>
+  <si>
+    <t>begin/end = "20260721"（对照组）</t>
+  </si>
+  <si>
+    <t>基准，无失败</t>
+  </si>
+  <si>
+    <t>begin/end = "XYZZY"</t>
+  </si>
+  <si>
+    <t>确定性失败 → TEMPORARILY_UNAVAILABLE</t>
+  </si>
+  <si>
+    <t>begin/end = "2026721"</t>
+  </si>
+  <si>
+    <t>begin/end = "abc"</t>
+  </si>
+  <si>
+    <t>begin/end = "20261332"</t>
+  </si>
+  <si>
+    <t>确定性失败 → TOOL_RUNTIME_ERROR</t>
+  </si>
+  <si>
+    <t>windcode = "999999.XX"（第一轮）</t>
+  </si>
+  <si>
+    <t>★ 非确定：4 次静默返回中证800 数据，4 次 MARKET_TARGET_NOT_FOUND</t>
   </si>
 </sst>
 </file>
@@ -1481,7 +1976,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" style="1" customWidth="1"/>
@@ -1598,6 +2093,38 @@
       </c>
       <c r="B14" s="1" t="s">
         <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -1625,31 +2152,31 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -1657,28 +2184,28 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -1686,28 +2213,28 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -1715,28 +2242,28 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>41</v>
-      </c>
       <c r="G4" s="1" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -1744,28 +2271,28 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="E5" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="I5" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -1773,28 +2300,28 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="E6" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="I6" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -1802,28 +2329,28 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="E7" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="I7" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
@@ -1831,28 +2358,28 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -1860,28 +2387,28 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
@@ -1889,28 +2416,28 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -1938,408 +2465,408 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>82</v>
-      </c>
       <c r="F8" s="1" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="E11" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="F11" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="F11" s="1" t="s">
-        <v>105</v>
-      </c>
       <c r="G11" s="1" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>82</v>
-      </c>
       <c r="F12" s="1" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
     </row>
   </sheetData>
@@ -2363,274 +2890,274 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>130</v>
-      </c>
       <c r="E5" s="1" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
     </row>
   </sheetData>
@@ -2660,37 +3187,37 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
@@ -2698,34 +3225,34 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="I2" s="1">
         <v>240</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -2733,34 +3260,34 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="I3" s="1">
         <v>480</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
@@ -2768,34 +3295,34 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="F4" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="G4" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="G4" s="1" t="s">
-        <v>184</v>
-      </c>
       <c r="H4" s="1" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="I4" s="1">
         <v>240</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
@@ -2803,34 +3330,34 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="I5" s="1">
         <v>480</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
@@ -2838,34 +3365,34 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="I6" s="1">
         <v>240</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
@@ -2873,34 +3400,34 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="I7" s="1">
         <v>480</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
@@ -2908,34 +3435,34 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="I8" s="1">
         <v>36</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
@@ -2943,34 +3470,34 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="I9" s="1">
         <v>36</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
@@ -2978,34 +3505,34 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="I10" s="1">
         <v>36</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
@@ -3013,34 +3540,34 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="I11" s="1">
         <v>1</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -3048,34 +3575,34 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="I12" s="1">
         <v>1</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -3083,34 +3610,34 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="I13" s="1">
         <v>1</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -3118,34 +3645,34 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
@@ -3153,34 +3680,34 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="I15" s="1">
         <v>480</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
@@ -3188,34 +3715,34 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
@@ -3223,34 +3750,34 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="I17" s="1">
         <v>36</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
@@ -3258,34 +3785,34 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="I18" s="1">
         <v>36</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
@@ -3293,34 +3820,34 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
@@ -3328,34 +3855,34 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
@@ -3363,34 +3890,34 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="I21" s="1">
         <v>36</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
@@ -3398,34 +3925,34 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="I22" s="1">
         <v>0</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
@@ -3433,34 +3960,34 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
@@ -3468,34 +3995,34 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="I24" s="1">
         <v>1</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
@@ -3503,34 +4030,34 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="I25" s="1">
         <v>1</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
@@ -3538,34 +4065,34 @@
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="I26" s="1">
         <v>1</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
@@ -3573,34 +4100,34 @@
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
@@ -3608,34 +4135,34 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="I28" s="1">
         <v>1</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
@@ -3643,34 +4170,34 @@
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="I29" s="1">
         <v>1</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
@@ -3678,34 +4205,34 @@
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="I30" s="1">
         <v>1</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
@@ -3713,34 +4240,34 @@
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="I31" s="1">
         <v>240</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
@@ -3748,34 +4275,34 @@
         <v>31</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="I32" s="1">
         <v>0</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
@@ -3783,34 +4310,34 @@
         <v>32</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
@@ -3818,34 +4345,34 @@
         <v>33</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="I34" s="1">
         <v>1</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
@@ -3853,34 +4380,34 @@
         <v>34</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
@@ -3888,34 +4415,34 @@
         <v>35</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="C36" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="H36" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="D36" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="G36" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="H36" s="1" t="s">
-        <v>280</v>
-      </c>
       <c r="I36" s="1" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>290</v>
+        <v>298</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
@@ -3923,34 +4450,34 @@
         <v>36</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="I37" s="1">
         <v>1</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
@@ -3958,34 +4485,34 @@
         <v>37</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="I38" s="1">
         <v>36</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
@@ -3993,34 +4520,34 @@
         <v>38</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="I39" s="1">
         <v>36</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
@@ -4028,34 +4555,34 @@
         <v>39</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="I40" s="1">
         <v>0</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
     </row>
   </sheetData>
@@ -4067,7 +4594,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -4080,25 +4607,25 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -4106,22 +4633,22 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>309</v>
+        <v>317</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -4129,22 +4656,22 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -4152,22 +4679,22 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>318</v>
+        <v>326</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -4175,22 +4702,22 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -4198,22 +4725,22 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>329</v>
+        <v>337</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -4221,22 +4748,22 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -4244,22 +4771,22 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>321</v>
+        <v>156</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -4267,22 +4794,22 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -4290,22 +4817,22 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -4313,22 +4840,22 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -4336,22 +4863,91 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="G12" s="1" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>356</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>376</v>
       </c>
     </row>
   </sheetData>
@@ -4359,4 +4955,1419 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D22"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="12" style="1" customWidth="1"/>
+    <col min="2" max="2" width="30" style="1" customWidth="1"/>
+    <col min="3" max="3" width="34" style="1" customWidth="1"/>
+    <col min="4" max="4" width="60" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>443</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:D1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:J28"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="5" style="1" customWidth="1"/>
+    <col min="2" max="2" width="8" style="1" customWidth="1"/>
+    <col min="3" max="4" width="26" style="1" customWidth="1"/>
+    <col min="5" max="5" width="52" style="1" customWidth="1"/>
+    <col min="6" max="6" width="8" style="1" customWidth="1"/>
+    <col min="7" max="7" width="26" style="1" customWidth="1"/>
+    <col min="8" max="8" width="7" style="1" customWidth="1"/>
+    <col min="9" max="10" width="30" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="H2" s="1">
+        <v>240</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="H3" s="1">
+        <v>240</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="H4" s="1">
+        <v>240</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="H6" s="1">
+        <v>240</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="H7" s="1">
+        <v>240</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="H8" s="1">
+        <v>240</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="H9" s="1">
+        <v>240</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="H10" s="1">
+        <v>240</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="H11" s="1">
+        <v>240</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="H13" s="1">
+        <v>240</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="H14" s="1">
+        <v>240</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="H17" s="1">
+        <v>240</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="H18" s="1">
+        <v>0</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="H19" s="1">
+        <v>720</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>19</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="H20" s="1">
+        <v>480</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>20</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="H21" s="1">
+        <v>720</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>21</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="H22" s="1">
+        <v>240</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>22</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="H23" s="1">
+        <v>0</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
+        <v>23</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="H24" s="1">
+        <v>31335</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
+        <v>24</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="H25" s="1">
+        <v>240</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
+        <v>25</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="H26" s="1">
+        <v>240</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
+        <v>26</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="H27" s="1">
+        <v>240</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" s="1">
+        <v>27</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="H28" s="1">
+        <v>240</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>449</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:J1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="42" style="1" customWidth="1"/>
+    <col min="2" max="2" width="10" style="1" customWidth="1"/>
+    <col min="3" max="4" width="8" style="1" customWidth="1"/>
+    <col min="5" max="5" width="56" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>503</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>504</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="B2" s="1">
+        <v>10</v>
+      </c>
+      <c r="C2" s="1">
+        <v>10</v>
+      </c>
+      <c r="D2" s="1">
+        <v>0</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="B3" s="1">
+        <v>15</v>
+      </c>
+      <c r="C3" s="1">
+        <v>14</v>
+      </c>
+      <c r="D3" s="1">
+        <v>1</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="B4" s="1">
+        <v>15</v>
+      </c>
+      <c r="C4" s="1">
+        <v>15</v>
+      </c>
+      <c r="D4" s="1">
+        <v>0</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="B5" s="1">
+        <v>3</v>
+      </c>
+      <c r="C5" s="1">
+        <v>0</v>
+      </c>
+      <c r="D5" s="1">
+        <v>3</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="B6" s="1">
+        <v>3</v>
+      </c>
+      <c r="C6" s="1">
+        <v>0</v>
+      </c>
+      <c r="D6" s="1">
+        <v>3</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="B7" s="1">
+        <v>3</v>
+      </c>
+      <c r="C7" s="1">
+        <v>0</v>
+      </c>
+      <c r="D7" s="1">
+        <v>3</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="B8" s="1">
+        <v>3</v>
+      </c>
+      <c r="C8" s="1">
+        <v>0</v>
+      </c>
+      <c r="D8" s="1">
+        <v>3</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="B9" s="1">
+        <v>8</v>
+      </c>
+      <c r="C9" s="1">
+        <v>4</v>
+      </c>
+      <c r="D9" s="1">
+        <v>4</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>520</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
 </file>
--- a/docs/wind-mcp-行情工具验证-20260721.xlsx
+++ b/docs/wind-mcp-行情工具验证-20260721.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7606" uniqueCount="1341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7544" uniqueCount="1325">
   <si>
     <t>项</t>
   </si>
@@ -2767,28 +2767,10 @@
     <t>string_keys</t>
   </si>
   <si>
-    <t>question</t>
-  </si>
-  <si>
     <t>必须是字符串且非空/非全空白</t>
   </si>
   <si>
-    <t>全部工具</t>
-  </si>
-  <si>
-    <t>query</t>
-  </si>
-  <si>
-    <t>executionMode</t>
-  </si>
-  <si>
-    <t>observation</t>
-  </si>
-  <si>
-    <t>no_whitespace_keys</t>
-  </si>
-  <si>
-    <t>不得含空格或其它空白字符</t>
+    <t>全部行情工具</t>
   </si>
   <si>
     <t>single_target_keys</t>
@@ -2806,18 +2788,6 @@
     <t>★ 不含 begin/end，故 quote 日期不受本地校验</t>
   </si>
   <si>
-    <t>beginDate</t>
-  </si>
-  <si>
-    <t>endDate</t>
-  </si>
-  <si>
-    <t>date</t>
-  </si>
-  <si>
-    <t>tradeDate</t>
-  </si>
-  <si>
     <t>kline</t>
   </si>
   <si>
@@ -2839,18 +2809,6 @@
     <t>字段 'issusp' 只能是 '0' 或 '1'</t>
   </si>
   <si>
-    <t>economic_edb</t>
-  </si>
-  <si>
-    <t>宏观 EDB 缺少必填字段时本地拦截</t>
-  </si>
-  <si>
-    <t>natural_language_get_edb_data</t>
-  </si>
-  <si>
-    <t>字段 'executionMode' 只能是 search/fetch/searchFetch 或 仅搜索/仅提数/搜索并提数</t>
-  </si>
-  <si>
     <t>规则表</t>
   </si>
   <si>
@@ -3329,12 +3287,6 @@
   </si>
   <si>
     <t>原因：参数值不合法。处理：按 references/tool-contracts.md 核对日期、枚举、windcode 等值；indexes 必须来自 references/indicators.md。重试：禁止原样重试；修正后最多重试一次。</t>
-  </si>
-  <si>
-    <t>EDB_INDICATOR_NOT_FOUND</t>
-  </si>
-  <si>
-    <t>原因：EDB 未找到用户想查询的经济指标。处理：保持 economic_data.natural_language_get_edb_data，只将 question 改成更短、更标准、更明确的单个指标名；优先补充官方口径、地区、来源或常见英文名，去掉年份、预测、市场规模、CAGR 或多个指标拼接等非指标名成分。重试：禁止原样重试；改写后最多重试一次。若改写后仍未找到，停止自动尝试并提示用户提供更明确的指标名称、来源或口径。</t>
   </si>
   <si>
     <t>MARKET_TARGET_NOT_FOUND</t>
@@ -5594,7 +5546,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="16" style="1" customWidth="1"/>
@@ -5629,13 +5581,13 @@
         <v>687</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>688</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>689</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>690</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -5646,13 +5598,13 @@
         <v>687</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>691</v>
+        <v>126</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>688</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>689</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>690</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -5660,16 +5612,16 @@
         <v>686</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>691</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>689</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>690</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -5677,16 +5629,16 @@
         <v>686</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>687</v>
+        <v>692</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>690</v>
+        <v>694</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -5694,322 +5646,118 @@
         <v>686</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>687</v>
+        <v>692</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>692</v>
+        <v>104</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>690</v>
+        <v>694</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>686</v>
+        <v>695</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>687</v>
+        <v>696</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>693</v>
+        <v>53</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>689</v>
+        <v>697</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>690</v>
+        <v>670</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>686</v>
+        <v>695</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>691</v>
+        <v>101</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>690</v>
+        <v>670</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>686</v>
+        <v>695</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>696</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>53</v>
+        <v>104</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>697</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>690</v>
+        <v>670</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>686</v>
+        <v>695</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>698</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>699</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>700</v>
+        <v>670</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>686</v>
+        <v>695</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>698</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>104</v>
+        <v>675</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>700</v>
+        <v>670</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>686</v>
+        <v>695</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>698</v>
       </c>
       <c r="C12" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>701</v>
       </c>
-      <c r="D12" s="1" t="s">
-        <v>699</v>
-      </c>
       <c r="E12" s="1" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>686</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>698</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>702</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>699</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>686</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>698</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>703</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>699</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>686</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>698</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>704</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>699</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>705</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>706</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>707</v>
-      </c>
-      <c r="E16" s="1" t="s">
         <v>670</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>705</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>706</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>707</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>705</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>706</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>707</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>705</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>708</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>709</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>705</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>708</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>675</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>710</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>705</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>708</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>711</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>712</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>706</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>692</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>713</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>714</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>712</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>706</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>688</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>713</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>714</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>712</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>708</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>692</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>715</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>714</v>
       </c>
     </row>
   </sheetData>
@@ -6033,30 +5781,30 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>716</v>
+        <v>702</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>718</v>
+        <v>704</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>719</v>
+        <v>705</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>720</v>
+        <v>706</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>721</v>
+        <v>707</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>111</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>722</v>
+        <v>708</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>642</v>
@@ -6067,13 +5815,13 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>721</v>
+        <v>707</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>111</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>723</v>
+        <v>709</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>642</v>
@@ -6084,13 +5832,13 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>721</v>
+        <v>707</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>111</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>724</v>
+        <v>710</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>642</v>
@@ -6101,16 +5849,16 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>721</v>
+        <v>707</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>111</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>725</v>
+        <v>711</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>726</v>
+        <v>712</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>63</v>
@@ -6118,16 +5866,16 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>721</v>
+        <v>707</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>111</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>727</v>
+        <v>713</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>726</v>
+        <v>712</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>63</v>
@@ -6135,16 +5883,16 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>721</v>
+        <v>707</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>111</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>728</v>
+        <v>714</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>726</v>
+        <v>712</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>63</v>
@@ -6152,16 +5900,16 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>721</v>
+        <v>707</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>111</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>729</v>
+        <v>715</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>730</v>
+        <v>716</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>63</v>
@@ -6169,16 +5917,16 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>721</v>
+        <v>707</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>111</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>731</v>
+        <v>717</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>730</v>
+        <v>716</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>63</v>
@@ -6186,16 +5934,16 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>721</v>
+        <v>707</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>111</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>732</v>
+        <v>718</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>730</v>
+        <v>716</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>63</v>
@@ -6203,16 +5951,16 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>721</v>
+        <v>707</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>111</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>733</v>
+        <v>719</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>734</v>
+        <v>720</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>63</v>
@@ -6220,16 +5968,16 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>721</v>
+        <v>707</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>111</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>735</v>
+        <v>721</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>734</v>
+        <v>720</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>63</v>
@@ -6237,16 +5985,16 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>721</v>
+        <v>707</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>111</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>736</v>
+        <v>722</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>734</v>
+        <v>720</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>63</v>
@@ -6254,16 +6002,16 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>721</v>
+        <v>707</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>111</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>737</v>
+        <v>723</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>738</v>
+        <v>724</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>63</v>
@@ -6271,16 +6019,16 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>721</v>
+        <v>707</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>111</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>739</v>
+        <v>725</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>738</v>
+        <v>724</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>63</v>
@@ -6288,16 +6036,16 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>721</v>
+        <v>707</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>111</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>740</v>
+        <v>726</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>738</v>
+        <v>724</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>63</v>
@@ -6305,16 +6053,16 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>721</v>
+        <v>707</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>111</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>741</v>
+        <v>727</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>742</v>
+        <v>728</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>63</v>
@@ -6322,16 +6070,16 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>721</v>
+        <v>707</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>111</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>743</v>
+        <v>729</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>742</v>
+        <v>728</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>63</v>
@@ -6339,16 +6087,16 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>721</v>
+        <v>707</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>111</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>744</v>
+        <v>730</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>742</v>
+        <v>728</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>63</v>
@@ -6356,16 +6104,16 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>721</v>
+        <v>707</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>111</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>745</v>
+        <v>731</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>742</v>
+        <v>728</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>63</v>
@@ -6373,16 +6121,16 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>721</v>
+        <v>707</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>111</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>746</v>
+        <v>732</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>747</v>
+        <v>733</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>63</v>
@@ -6390,16 +6138,16 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>721</v>
+        <v>707</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>111</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>748</v>
+        <v>734</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>747</v>
+        <v>733</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>63</v>
@@ -6407,16 +6155,16 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>721</v>
+        <v>707</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>111</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>749</v>
+        <v>735</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>747</v>
+        <v>733</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>63</v>
@@ -6424,16 +6172,16 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>721</v>
+        <v>707</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>111</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>750</v>
+        <v>736</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>747</v>
+        <v>733</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>63</v>
@@ -6441,13 +6189,13 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>721</v>
+        <v>707</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>111</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>751</v>
+        <v>737</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>269</v>
@@ -6458,13 +6206,13 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>721</v>
+        <v>707</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>111</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>752</v>
+        <v>738</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>269</v>
@@ -6475,13 +6223,13 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>721</v>
+        <v>707</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>111</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>753</v>
+        <v>739</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>269</v>
@@ -6492,13 +6240,13 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>721</v>
+        <v>707</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>111</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>754</v>
+        <v>740</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>269</v>
@@ -6509,16 +6257,16 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>721</v>
+        <v>707</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>111</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>755</v>
+        <v>741</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>756</v>
+        <v>742</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>63</v>
@@ -6526,16 +6274,16 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>721</v>
+        <v>707</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>111</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>757</v>
+        <v>743</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>756</v>
+        <v>742</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>63</v>
@@ -6543,16 +6291,16 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>721</v>
+        <v>707</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>111</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>758</v>
+        <v>744</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>756</v>
+        <v>742</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>63</v>
@@ -6560,16 +6308,16 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>721</v>
+        <v>707</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>111</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>759</v>
+        <v>745</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>756</v>
+        <v>742</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>63</v>
@@ -6577,16 +6325,16 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>721</v>
+        <v>707</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>111</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>760</v>
+        <v>746</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>756</v>
+        <v>742</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>63</v>
@@ -6594,16 +6342,16 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>721</v>
+        <v>707</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>111</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>761</v>
+        <v>747</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>756</v>
+        <v>742</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>63</v>
@@ -6611,16 +6359,16 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>721</v>
+        <v>707</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>111</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>762</v>
+        <v>748</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>763</v>
+        <v>749</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>63</v>
@@ -6628,16 +6376,16 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>721</v>
+        <v>707</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>111</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>764</v>
+        <v>750</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>763</v>
+        <v>749</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>63</v>
@@ -6645,16 +6393,16 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>721</v>
+        <v>707</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>111</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>765</v>
+        <v>751</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>763</v>
+        <v>749</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>63</v>
@@ -6662,16 +6410,16 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>721</v>
+        <v>707</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>111</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>766</v>
+        <v>752</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>763</v>
+        <v>749</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>63</v>
@@ -6679,16 +6427,16 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>721</v>
+        <v>707</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>111</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>767</v>
+        <v>753</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>763</v>
+        <v>749</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>63</v>
@@ -6696,16 +6444,16 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>721</v>
+        <v>707</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>111</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>768</v>
+        <v>754</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>763</v>
+        <v>749</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>63</v>
@@ -6713,16 +6461,16 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>721</v>
+        <v>707</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>111</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>769</v>
+        <v>755</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>770</v>
+        <v>756</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>63</v>
@@ -6730,16 +6478,16 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>721</v>
+        <v>707</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>111</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>770</v>
+        <v>756</v>
       </c>
       <c r="E42" s="1" t="s">
         <v>63</v>
@@ -6747,16 +6495,16 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>721</v>
+        <v>707</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>111</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>772</v>
+        <v>758</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>770</v>
+        <v>756</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>63</v>
@@ -6764,16 +6512,16 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>721</v>
+        <v>707</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>111</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>773</v>
+        <v>759</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>770</v>
+        <v>756</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>63</v>
@@ -6781,16 +6529,16 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>721</v>
+        <v>707</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>111</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>774</v>
+        <v>760</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>770</v>
+        <v>756</v>
       </c>
       <c r="E45" s="1" t="s">
         <v>63</v>
@@ -6798,16 +6546,16 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>721</v>
+        <v>707</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>111</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>775</v>
+        <v>761</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>770</v>
+        <v>756</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>63</v>
@@ -6815,16 +6563,16 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>721</v>
+        <v>707</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>111</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>776</v>
+        <v>762</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>777</v>
+        <v>763</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>63</v>
@@ -6832,16 +6580,16 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>721</v>
+        <v>707</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>111</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>778</v>
+        <v>764</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>777</v>
+        <v>763</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>63</v>
@@ -6849,16 +6597,16 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>721</v>
+        <v>707</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>111</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>779</v>
+        <v>765</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>777</v>
+        <v>763</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>63</v>
@@ -6866,16 +6614,16 @@
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>721</v>
+        <v>707</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>111</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>780</v>
+        <v>766</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>777</v>
+        <v>763</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>63</v>
@@ -6883,16 +6631,16 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>721</v>
+        <v>707</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>111</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>781</v>
+        <v>767</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>777</v>
+        <v>763</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>63</v>
@@ -6900,16 +6648,16 @@
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>721</v>
+        <v>707</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>111</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>782</v>
+        <v>768</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>777</v>
+        <v>763</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>63</v>
@@ -6917,16 +6665,16 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>721</v>
+        <v>707</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>111</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>783</v>
+        <v>769</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>784</v>
+        <v>770</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>63</v>
@@ -6934,16 +6682,16 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>721</v>
+        <v>707</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>111</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>785</v>
+        <v>771</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>784</v>
+        <v>770</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>63</v>
@@ -6951,16 +6699,16 @@
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>721</v>
+        <v>707</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>111</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>786</v>
+        <v>772</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>784</v>
+        <v>770</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>63</v>
@@ -6968,16 +6716,16 @@
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>721</v>
+        <v>707</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>111</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>787</v>
+        <v>773</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>784</v>
+        <v>770</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>63</v>
@@ -6985,16 +6733,16 @@
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>721</v>
+        <v>707</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>111</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>788</v>
+        <v>774</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>784</v>
+        <v>770</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>63</v>
@@ -7002,16 +6750,16 @@
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>721</v>
+        <v>707</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>111</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>789</v>
+        <v>775</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>790</v>
+        <v>776</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>63</v>
@@ -7019,16 +6767,16 @@
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>721</v>
+        <v>707</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>111</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>791</v>
+        <v>777</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>790</v>
+        <v>776</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>63</v>
@@ -7036,16 +6784,16 @@
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>721</v>
+        <v>707</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>111</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>792</v>
+        <v>778</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>790</v>
+        <v>776</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>63</v>
@@ -7053,16 +6801,16 @@
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>721</v>
+        <v>707</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>111</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>793</v>
+        <v>779</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>790</v>
+        <v>776</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>63</v>
@@ -7070,13 +6818,13 @@
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>794</v>
+        <v>780</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>795</v>
+        <v>781</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>796</v>
+        <v>782</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>233</v>
@@ -7087,13 +6835,13 @@
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>794</v>
+        <v>780</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>795</v>
+        <v>781</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>797</v>
+        <v>783</v>
       </c>
       <c r="D63" s="1" t="s">
         <v>233</v>
@@ -7104,13 +6852,13 @@
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>794</v>
+        <v>780</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>795</v>
+        <v>781</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>798</v>
+        <v>784</v>
       </c>
       <c r="D64" s="1" t="s">
         <v>233</v>
@@ -7121,13 +6869,13 @@
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>794</v>
+        <v>780</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>795</v>
+        <v>781</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>799</v>
+        <v>785</v>
       </c>
       <c r="D65" s="1" t="s">
         <v>233</v>
@@ -7138,13 +6886,13 @@
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>794</v>
+        <v>780</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>795</v>
+        <v>781</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>800</v>
+        <v>786</v>
       </c>
       <c r="D66" s="1" t="s">
         <v>233</v>
@@ -7155,13 +6903,13 @@
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>794</v>
+        <v>780</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>795</v>
+        <v>781</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>801</v>
+        <v>787</v>
       </c>
       <c r="D67" s="1" t="s">
         <v>233</v>
@@ -7172,13 +6920,13 @@
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>794</v>
+        <v>780</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>795</v>
+        <v>781</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>802</v>
+        <v>788</v>
       </c>
       <c r="D68" s="1" t="s">
         <v>233</v>
@@ -7189,13 +6937,13 @@
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>794</v>
+        <v>780</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>795</v>
+        <v>781</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>803</v>
+        <v>789</v>
       </c>
       <c r="D69" s="1" t="s">
         <v>235</v>
@@ -7206,13 +6954,13 @@
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>794</v>
+        <v>780</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>795</v>
+        <v>781</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>804</v>
+        <v>790</v>
       </c>
       <c r="D70" s="1" t="s">
         <v>235</v>
@@ -7223,13 +6971,13 @@
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>794</v>
+        <v>780</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>795</v>
+        <v>781</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>805</v>
+        <v>791</v>
       </c>
       <c r="D71" s="1" t="s">
         <v>235</v>
@@ -7240,13 +6988,13 @@
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>794</v>
+        <v>780</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>795</v>
+        <v>781</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>806</v>
+        <v>792</v>
       </c>
       <c r="D72" s="1" t="s">
         <v>235</v>
@@ -7257,13 +7005,13 @@
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>794</v>
+        <v>780</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>795</v>
+        <v>781</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>807</v>
+        <v>793</v>
       </c>
       <c r="D73" s="1" t="s">
         <v>235</v>
@@ -7274,13 +7022,13 @@
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
+        <v>780</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>781</v>
+      </c>
+      <c r="C74" s="1" t="s">
         <v>794</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>795</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>808</v>
       </c>
       <c r="D74" s="1" t="s">
         <v>235</v>
@@ -7291,13 +7039,13 @@
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>794</v>
+        <v>780</v>
       </c>
       <c r="B75" s="1" t="s">
+        <v>781</v>
+      </c>
+      <c r="C75" s="1" t="s">
         <v>795</v>
-      </c>
-      <c r="C75" s="1" t="s">
-        <v>809</v>
       </c>
       <c r="D75" s="1" t="s">
         <v>237</v>
@@ -7308,13 +7056,13 @@
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>794</v>
+        <v>780</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>795</v>
+        <v>781</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>810</v>
+        <v>796</v>
       </c>
       <c r="D76" s="1" t="s">
         <v>237</v>
@@ -7325,13 +7073,13 @@
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>794</v>
+        <v>780</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>795</v>
+        <v>781</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>811</v>
+        <v>797</v>
       </c>
       <c r="D77" s="1" t="s">
         <v>237</v>
@@ -7342,13 +7090,13 @@
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>794</v>
+        <v>780</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>795</v>
+        <v>781</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>812</v>
+        <v>798</v>
       </c>
       <c r="D78" s="1" t="s">
         <v>296</v>
@@ -7359,13 +7107,13 @@
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>794</v>
+        <v>780</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>795</v>
+        <v>781</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>813</v>
+        <v>799</v>
       </c>
       <c r="D79" s="1" t="s">
         <v>296</v>
@@ -7376,13 +7124,13 @@
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>794</v>
+        <v>780</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>795</v>
+        <v>781</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>814</v>
+        <v>800</v>
       </c>
       <c r="D80" s="1" t="s">
         <v>297</v>
@@ -7393,13 +7141,13 @@
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>794</v>
+        <v>780</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>795</v>
+        <v>781</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>815</v>
+        <v>801</v>
       </c>
       <c r="D81" s="1" t="s">
         <v>297</v>
@@ -7410,13 +7158,13 @@
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>794</v>
+        <v>780</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>795</v>
+        <v>781</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>816</v>
+        <v>802</v>
       </c>
       <c r="D82" s="1" t="s">
         <v>238</v>
@@ -7427,13 +7175,13 @@
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>794</v>
+        <v>780</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>795</v>
+        <v>781</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>817</v>
+        <v>803</v>
       </c>
       <c r="D83" s="1" t="s">
         <v>238</v>
@@ -7444,13 +7192,13 @@
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>794</v>
+        <v>780</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>795</v>
+        <v>781</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>818</v>
+        <v>804</v>
       </c>
       <c r="D84" s="1" t="s">
         <v>322</v>
@@ -7461,13 +7209,13 @@
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>794</v>
+        <v>780</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>795</v>
+        <v>781</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>819</v>
+        <v>805</v>
       </c>
       <c r="D85" s="1" t="s">
         <v>322</v>
@@ -7478,13 +7226,13 @@
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>794</v>
+        <v>780</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>795</v>
+        <v>781</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>820</v>
+        <v>806</v>
       </c>
       <c r="D86" s="1" t="s">
         <v>240</v>
@@ -7495,13 +7243,13 @@
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>794</v>
+        <v>780</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>795</v>
+        <v>781</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>821</v>
+        <v>807</v>
       </c>
       <c r="D87" s="1" t="s">
         <v>240</v>
@@ -7512,13 +7260,13 @@
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>794</v>
+        <v>780</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>795</v>
+        <v>781</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>822</v>
+        <v>808</v>
       </c>
       <c r="D88" s="1" t="s">
         <v>240</v>
@@ -7529,13 +7277,13 @@
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>794</v>
+        <v>780</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>795</v>
+        <v>781</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>823</v>
+        <v>809</v>
       </c>
       <c r="D89" s="1" t="s">
         <v>240</v>
@@ -7546,13 +7294,13 @@
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>794</v>
+        <v>780</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>795</v>
+        <v>781</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>824</v>
+        <v>810</v>
       </c>
       <c r="D90" s="1" t="s">
         <v>329</v>
@@ -7563,13 +7311,13 @@
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>794</v>
+        <v>780</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>795</v>
+        <v>781</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>825</v>
+        <v>811</v>
       </c>
       <c r="D91" s="1" t="s">
         <v>329</v>
@@ -7580,13 +7328,13 @@
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>794</v>
+        <v>780</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>795</v>
+        <v>781</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>826</v>
+        <v>812</v>
       </c>
       <c r="D92" s="1" t="s">
         <v>244</v>
@@ -7597,13 +7345,13 @@
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>794</v>
+        <v>780</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>795</v>
+        <v>781</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>827</v>
+        <v>813</v>
       </c>
       <c r="D93" s="1" t="s">
         <v>244</v>
@@ -7614,13 +7362,13 @@
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>794</v>
+        <v>780</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>795</v>
+        <v>781</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>828</v>
+        <v>814</v>
       </c>
       <c r="D94" s="1" t="s">
         <v>244</v>
@@ -7631,13 +7379,13 @@
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>794</v>
+        <v>780</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>795</v>
+        <v>781</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>829</v>
+        <v>815</v>
       </c>
       <c r="D95" s="1" t="s">
         <v>244</v>
@@ -7648,13 +7396,13 @@
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>794</v>
+        <v>780</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>795</v>
+        <v>781</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>830</v>
+        <v>816</v>
       </c>
       <c r="D96" s="1" t="s">
         <v>337</v>
@@ -7665,13 +7413,13 @@
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>794</v>
+        <v>780</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>795</v>
+        <v>781</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>831</v>
+        <v>817</v>
       </c>
       <c r="D97" s="1" t="s">
         <v>336</v>
@@ -7682,13 +7430,13 @@
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>794</v>
+        <v>780</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>795</v>
+        <v>781</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>832</v>
+        <v>818</v>
       </c>
       <c r="D98" s="1" t="s">
         <v>337</v>
@@ -7699,13 +7447,13 @@
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>794</v>
+        <v>780</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>795</v>
+        <v>781</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>833</v>
+        <v>819</v>
       </c>
       <c r="D99" s="1" t="s">
         <v>556</v>
@@ -7716,13 +7464,13 @@
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>794</v>
+        <v>780</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>795</v>
+        <v>781</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>834</v>
+        <v>820</v>
       </c>
       <c r="D100" s="1" t="s">
         <v>556</v>
@@ -7733,13 +7481,13 @@
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>794</v>
+        <v>780</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>795</v>
+        <v>781</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>835</v>
+        <v>821</v>
       </c>
       <c r="D101" s="1" t="s">
         <v>348</v>
@@ -7750,13 +7498,13 @@
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>794</v>
+        <v>780</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>795</v>
+        <v>781</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>836</v>
+        <v>822</v>
       </c>
       <c r="D102" s="1" t="s">
         <v>557</v>
@@ -7767,13 +7515,13 @@
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>794</v>
+        <v>780</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>795</v>
+        <v>781</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>837</v>
+        <v>823</v>
       </c>
       <c r="D103" s="1" t="s">
         <v>557</v>
@@ -7784,13 +7532,13 @@
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>794</v>
+        <v>780</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>795</v>
+        <v>781</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>838</v>
+        <v>824</v>
       </c>
       <c r="D104" s="1" t="s">
         <v>369</v>
@@ -7801,13 +7549,13 @@
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>794</v>
+        <v>780</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>795</v>
+        <v>781</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>839</v>
+        <v>825</v>
       </c>
       <c r="D105" s="1" t="s">
         <v>369</v>
@@ -7818,13 +7566,13 @@
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>794</v>
+        <v>780</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>795</v>
+        <v>781</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>840</v>
+        <v>826</v>
       </c>
       <c r="D106" s="1" t="s">
         <v>369</v>
@@ -7835,13 +7583,13 @@
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>794</v>
+        <v>780</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>795</v>
+        <v>781</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>841</v>
+        <v>827</v>
       </c>
       <c r="D107" s="1" t="s">
         <v>369</v>
@@ -7852,291 +7600,291 @@
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>842</v>
+        <v>828</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>53</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>843</v>
+        <v>829</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>844</v>
+        <v>830</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>845</v>
+        <v>831</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
-        <v>842</v>
+        <v>828</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>53</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>846</v>
+        <v>832</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>844</v>
+        <v>830</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>845</v>
+        <v>831</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>842</v>
+        <v>828</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>53</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>847</v>
+        <v>833</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>844</v>
+        <v>830</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>845</v>
+        <v>831</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>842</v>
+        <v>828</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>53</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>848</v>
+        <v>834</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>844</v>
+        <v>830</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>845</v>
+        <v>831</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>842</v>
+        <v>828</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>53</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>849</v>
+        <v>835</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>850</v>
+        <v>836</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>845</v>
+        <v>831</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>842</v>
+        <v>828</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>53</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>851</v>
+        <v>837</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>850</v>
+        <v>836</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>845</v>
+        <v>831</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>842</v>
+        <v>828</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>53</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>852</v>
+        <v>838</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>850</v>
+        <v>836</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>845</v>
+        <v>831</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>842</v>
+        <v>828</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>53</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>853</v>
+        <v>839</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>854</v>
+        <v>840</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>845</v>
+        <v>831</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>842</v>
+        <v>828</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>53</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>855</v>
+        <v>841</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>854</v>
+        <v>840</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>845</v>
+        <v>831</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>842</v>
+        <v>828</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>53</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>856</v>
+        <v>842</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>854</v>
+        <v>840</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>845</v>
+        <v>831</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>842</v>
+        <v>828</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>53</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>857</v>
+        <v>843</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>858</v>
+        <v>844</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>845</v>
+        <v>831</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>842</v>
+        <v>828</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>53</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>859</v>
+        <v>845</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>858</v>
+        <v>844</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>845</v>
+        <v>831</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
-        <v>842</v>
+        <v>828</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>53</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>860</v>
+        <v>846</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>861</v>
+        <v>847</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>845</v>
+        <v>831</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
-        <v>842</v>
+        <v>828</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>53</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>862</v>
+        <v>848</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>861</v>
+        <v>847</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>845</v>
+        <v>831</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
-        <v>842</v>
+        <v>828</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>53</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>863</v>
+        <v>849</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>864</v>
+        <v>850</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>845</v>
+        <v>831</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
-        <v>842</v>
+        <v>828</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>53</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>865</v>
+        <v>851</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>864</v>
+        <v>850</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>845</v>
+        <v>831</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
-        <v>842</v>
+        <v>828</v>
       </c>
       <c r="B124" s="1" t="s">
         <v>53</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>866</v>
+        <v>852</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>867</v>
+        <v>853</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>845</v>
+        <v>831</v>
       </c>
     </row>
   </sheetData>
@@ -8148,7 +7896,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="28" style="1" customWidth="1"/>
@@ -8157,154 +7905,146 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>868</v>
+        <v>854</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>869</v>
+        <v>855</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>870</v>
+        <v>856</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>871</v>
+        <v>857</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>872</v>
+        <v>858</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>873</v>
+        <v>859</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>874</v>
+        <v>860</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>875</v>
+        <v>861</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>876</v>
+        <v>862</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>877</v>
+        <v>863</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>878</v>
+        <v>864</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>879</v>
+        <v>865</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>880</v>
+        <v>866</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>881</v>
+        <v>867</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>882</v>
+        <v>868</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>883</v>
+        <v>869</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>884</v>
+        <v>870</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>885</v>
+        <v>871</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>886</v>
+        <v>872</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>887</v>
+        <v>873</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>888</v>
+        <v>874</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>889</v>
+        <v>875</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>890</v>
+        <v>876</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>891</v>
+        <v>877</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>892</v>
+        <v>878</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>893</v>
+        <v>879</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>894</v>
+        <v>880</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>895</v>
+        <v>881</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>896</v>
+        <v>882</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>897</v>
+        <v>883</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>898</v>
+        <v>884</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>899</v>
+        <v>885</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>900</v>
+        <v>886</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>901</v>
+        <v>887</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>902</v>
+        <v>888</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>903</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>904</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>905</v>
+        <v>889</v>
       </c>
     </row>
   </sheetData>
@@ -8328,19 +8068,19 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>906</v>
+        <v>890</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>79</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>907</v>
+        <v>891</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>908</v>
+        <v>892</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>909</v>
+        <v>893</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -8348,16 +8088,16 @@
         <v>671</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>910</v>
+        <v>894</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>911</v>
+        <v>895</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>912</v>
+        <v>896</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>913</v>
+        <v>897</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -8371,10 +8111,10 @@
         <v>82</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>914</v>
+        <v>898</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>915</v>
+        <v>899</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -8382,16 +8122,16 @@
         <v>667</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>916</v>
+        <v>900</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>917</v>
+        <v>901</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>918</v>
+        <v>902</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>919</v>
+        <v>903</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -8399,16 +8139,16 @@
         <v>667</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>916</v>
+        <v>900</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>920</v>
+        <v>904</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>921</v>
+        <v>905</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>922</v>
+        <v>906</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -8416,16 +8156,16 @@
         <v>671</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>923</v>
+        <v>907</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>924</v>
+        <v>908</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>925</v>
+        <v>909</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>926</v>
+        <v>910</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -8436,13 +8176,13 @@
         <v>107</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>927</v>
+        <v>911</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>928</v>
+        <v>912</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>929</v>
+        <v>913</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -8453,47 +8193,47 @@
         <v>111</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>930</v>
+        <v>914</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>931</v>
+        <v>915</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>932</v>
+        <v>916</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>845</v>
+        <v>831</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>53</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>933</v>
+        <v>917</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>934</v>
+        <v>918</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>935</v>
+        <v>919</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>936</v>
+        <v>920</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>147</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>937</v>
+        <v>921</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>938</v>
+        <v>922</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>939</v>
+        <v>923</v>
       </c>
     </row>
   </sheetData>
@@ -8533,19 +8273,19 @@
         <v>82</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>940</v>
+        <v>924</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>941</v>
+        <v>925</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>942</v>
+        <v>926</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>943</v>
+        <v>927</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>944</v>
+        <v>928</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -8568,10 +8308,10 @@
         <v>86</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>945</v>
+        <v>929</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>946</v>
+        <v>930</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>56</v>
@@ -8597,13 +8337,13 @@
         <v>669</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>947</v>
+        <v>931</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>948</v>
+        <v>932</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>949</v>
+        <v>933</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -8629,10 +8369,10 @@
         <v>95</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>948</v>
+        <v>932</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>950</v>
+        <v>934</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -8655,10 +8395,10 @@
         <v>86</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>945</v>
+        <v>929</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>951</v>
+        <v>935</v>
       </c>
       <c r="I5" s="1" t="s">
         <v>56</v>
@@ -8687,7 +8427,7 @@
         <v>102</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>952</v>
+        <v>936</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>56</v>
@@ -8716,7 +8456,7 @@
         <v>105</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>953</v>
+        <v>937</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>56</v>
@@ -8739,16 +8479,16 @@
         <v>668</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>954</v>
+        <v>938</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>955</v>
+        <v>939</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>956</v>
+        <v>940</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>957</v>
+        <v>941</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -8768,13 +8508,13 @@
         <v>673</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>958</v>
+        <v>942</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>959</v>
+        <v>943</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>960</v>
+        <v>944</v>
       </c>
       <c r="I9" s="1" t="s">
         <v>56</v>
@@ -8797,13 +8537,13 @@
         <v>676</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>958</v>
+        <v>942</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>961</v>
+        <v>945</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>962</v>
+        <v>946</v>
       </c>
       <c r="I10" s="1" t="s">
         <v>75</v>
@@ -8826,13 +8566,13 @@
         <v>678</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>958</v>
+        <v>942</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>963</v>
+        <v>947</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>962</v>
+        <v>946</v>
       </c>
       <c r="I11" s="1" t="s">
         <v>75</v>
@@ -8858,10 +8598,10 @@
         <v>669</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>964</v>
+        <v>948</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>962</v>
+        <v>946</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>75</v>
@@ -8872,7 +8612,7 @@
         <v>72</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>965</v>
+        <v>949</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>53</v>
@@ -8887,13 +8627,13 @@
         <v>86</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>945</v>
+        <v>929</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>966</v>
+        <v>950</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>967</v>
+        <v>951</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
@@ -8901,7 +8641,7 @@
         <v>72</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>965</v>
+        <v>949</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>126</v>
@@ -8916,13 +8656,13 @@
         <v>86</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>968</v>
+        <v>952</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>969</v>
+        <v>953</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>970</v>
+        <v>954</v>
       </c>
     </row>
   </sheetData>
@@ -8946,24 +8686,24 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>971</v>
+        <v>955</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>972</v>
+        <v>956</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>140</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>973</v>
+        <v>957</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>942</v>
+        <v>926</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>974</v>
+        <v>958</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>145</v>
@@ -8972,15 +8712,15 @@
         <v>86</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>975</v>
+        <v>959</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>976</v>
+        <v>960</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>974</v>
+        <v>958</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>147</v>
@@ -8989,24 +8729,24 @@
         <v>86</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>975</v>
+        <v>959</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>977</v>
+        <v>961</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>978</v>
+        <v>962</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>979</v>
+        <v>963</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>150</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>975</v>
+        <v>959</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>151</v>
@@ -9014,16 +8754,16 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>978</v>
+        <v>962</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>980</v>
+        <v>964</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>981</v>
+        <v>965</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>975</v>
+        <v>959</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>154</v>
@@ -9031,92 +8771,92 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>982</v>
+        <v>966</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>983</v>
+        <v>967</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>143</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>975</v>
+        <v>959</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>984</v>
+        <v>968</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>982</v>
+        <v>966</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>985</v>
+        <v>969</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>143</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>975</v>
+        <v>959</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>986</v>
+        <v>970</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>982</v>
+        <v>966</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>987</v>
+        <v>971</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>86</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>988</v>
+        <v>972</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>989</v>
+        <v>973</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>982</v>
+        <v>966</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>990</v>
+        <v>974</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>150</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>991</v>
+        <v>975</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>992</v>
+        <v>976</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>993</v>
+        <v>977</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>994</v>
+        <v>978</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>75</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>988</v>
+        <v>972</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>995</v>
+        <v>979</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>996</v>
+        <v>980</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>179</v>
@@ -9125,49 +8865,49 @@
         <v>86</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>997</v>
+        <v>981</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>998</v>
+        <v>982</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>996</v>
+        <v>980</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>999</v>
+        <v>983</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>86</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>997</v>
+        <v>981</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>1000</v>
+        <v>984</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>996</v>
+        <v>980</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>1001</v>
+        <v>985</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>86</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>997</v>
+        <v>981</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>1002</v>
+        <v>986</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>996</v>
+        <v>980</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>174</v>
@@ -9176,44 +8916,44 @@
         <v>86</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>997</v>
+        <v>981</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>1003</v>
+        <v>987</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>993</v>
+        <v>977</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>1004</v>
+        <v>988</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>75</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>1005</v>
+        <v>989</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>1006</v>
+        <v>990</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>1007</v>
+        <v>991</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>1008</v>
+        <v>992</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>75</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>705</v>
+        <v>695</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>1009</v>
+        <v>993</v>
       </c>
     </row>
   </sheetData>
@@ -9246,10 +8986,10 @@
         <v>40</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>1010</v>
+        <v>994</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>1011</v>
+        <v>995</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>41</v>
@@ -9258,22 +8998,22 @@
         <v>42</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>1012</v>
+        <v>996</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>1013</v>
+        <v>997</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>1014</v>
+        <v>998</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>1015</v>
+        <v>999</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>1016</v>
+        <v>1000</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>1017</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
@@ -9281,10 +9021,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>1018</v>
+        <v>1002</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>1019</v>
+        <v>1003</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>49</v>
@@ -9293,10 +9033,10 @@
         <v>50</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>1020</v>
+        <v>1004</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>1021</v>
+        <v>1005</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>88</v>
@@ -9305,10 +9045,10 @@
         <v>240</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>1022</v>
+        <v>1006</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>1023</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -9316,10 +9056,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1018</v>
+        <v>1002</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>1024</v>
+        <v>1008</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>49</v>
@@ -9328,10 +9068,10 @@
         <v>50</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>1025</v>
+        <v>1009</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>1021</v>
+        <v>1005</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>88</v>
@@ -9340,10 +9080,10 @@
         <v>480</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>1022</v>
+        <v>1006</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>1026</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
@@ -9351,10 +9091,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>1018</v>
+        <v>1002</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>1027</v>
+        <v>1011</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>57</v>
@@ -9363,10 +9103,10 @@
         <v>58</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>1028</v>
+        <v>1012</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>1021</v>
+        <v>1005</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>88</v>
@@ -9375,10 +9115,10 @@
         <v>240</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>1022</v>
+        <v>1006</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>1029</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
@@ -9386,10 +9126,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>1018</v>
+        <v>1002</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>1030</v>
+        <v>1014</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>57</v>
@@ -9398,10 +9138,10 @@
         <v>58</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>1031</v>
+        <v>1015</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>1021</v>
+        <v>1005</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>88</v>
@@ -9410,10 +9150,10 @@
         <v>480</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>1022</v>
+        <v>1006</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>1032</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
@@ -9421,10 +9161,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>1018</v>
+        <v>1002</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>1033</v>
+        <v>1017</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>60</v>
@@ -9433,10 +9173,10 @@
         <v>61</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>1034</v>
+        <v>1018</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>1021</v>
+        <v>1005</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>88</v>
@@ -9445,10 +9185,10 @@
         <v>240</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>1022</v>
+        <v>1006</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>1035</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
@@ -9456,10 +9196,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>1018</v>
+        <v>1002</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>1036</v>
+        <v>1020</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>60</v>
@@ -9468,10 +9208,10 @@
         <v>61</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>1037</v>
+        <v>1021</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>1021</v>
+        <v>1005</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>88</v>
@@ -9480,10 +9220,10 @@
         <v>480</v>
       </c>
       <c r="J7" s="1" t="s">
+        <v>1006</v>
+      </c>
+      <c r="K7" s="1" t="s">
         <v>1022</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>1038</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
@@ -9491,10 +9231,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>1018</v>
+        <v>1002</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>1039</v>
+        <v>1023</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>49</v>
@@ -9503,10 +9243,10 @@
         <v>62</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>1040</v>
+        <v>1024</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>1021</v>
+        <v>1005</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>88</v>
@@ -9515,10 +9255,10 @@
         <v>36</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>1022</v>
+        <v>1006</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>1041</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
@@ -9526,10 +9266,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>1018</v>
+        <v>1002</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>1042</v>
+        <v>1026</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>57</v>
@@ -9538,10 +9278,10 @@
         <v>68</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>1043</v>
+        <v>1027</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>1021</v>
+        <v>1005</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>88</v>
@@ -9550,10 +9290,10 @@
         <v>36</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>1022</v>
+        <v>1006</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>1044</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
@@ -9561,10 +9301,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>1018</v>
+        <v>1002</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>1045</v>
+        <v>1029</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>60</v>
@@ -9573,10 +9313,10 @@
         <v>70</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>1046</v>
+        <v>1030</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>1021</v>
+        <v>1005</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>88</v>
@@ -9585,10 +9325,10 @@
         <v>36</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>1022</v>
+        <v>1006</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>1047</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
@@ -9596,10 +9336,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>1018</v>
+        <v>1002</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>1048</v>
+        <v>1032</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>49</v>
@@ -9608,10 +9348,10 @@
         <v>71</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>1049</v>
+        <v>1033</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>1021</v>
+        <v>1005</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>88</v>
@@ -9620,10 +9360,10 @@
         <v>1</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>1050</v>
+        <v>1034</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>1051</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -9631,10 +9371,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>1018</v>
+        <v>1002</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>1052</v>
+        <v>1036</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>57</v>
@@ -9643,10 +9383,10 @@
         <v>77</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>1053</v>
+        <v>1037</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>1021</v>
+        <v>1005</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>88</v>
@@ -9655,10 +9395,10 @@
         <v>1</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>1054</v>
+        <v>1038</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>1055</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -9666,10 +9406,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>1018</v>
+        <v>1002</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>1056</v>
+        <v>1040</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>60</v>
@@ -9678,10 +9418,10 @@
         <v>78</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>1057</v>
+        <v>1041</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>1021</v>
+        <v>1005</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>88</v>
@@ -9690,10 +9430,10 @@
         <v>1</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>1050</v>
+        <v>1034</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>1058</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -9701,10 +9441,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>1059</v>
+        <v>1043</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>1060</v>
+        <v>1044</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>49</v>
@@ -9713,13 +9453,13 @@
         <v>50</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>1061</v>
+        <v>1045</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>1062</v>
+        <v>1046</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>870</v>
+        <v>856</v>
       </c>
       <c r="I14" s="1" t="s">
         <v>88</v>
@@ -9728,7 +9468,7 @@
         <v>88</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>1063</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
@@ -9736,10 +9476,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>1059</v>
+        <v>1043</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>1064</v>
+        <v>1048</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>49</v>
@@ -9748,10 +9488,10 @@
         <v>50</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>1065</v>
+        <v>1049</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>1021</v>
+        <v>1005</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>88</v>
@@ -9760,10 +9500,10 @@
         <v>480</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>1022</v>
+        <v>1006</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>1026</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
@@ -9771,10 +9511,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>1059</v>
+        <v>1043</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>1066</v>
+        <v>1050</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>49</v>
@@ -9783,13 +9523,13 @@
         <v>62</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>1067</v>
+        <v>1051</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>1062</v>
+        <v>1046</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>890</v>
+        <v>874</v>
       </c>
       <c r="I16" s="1" t="s">
         <v>88</v>
@@ -9798,7 +9538,7 @@
         <v>88</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>1068</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
@@ -9806,10 +9546,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>1059</v>
+        <v>1043</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>1069</v>
+        <v>1053</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>49</v>
@@ -9818,10 +9558,10 @@
         <v>62</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>1070</v>
+        <v>1054</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>1021</v>
+        <v>1005</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>88</v>
@@ -9830,10 +9570,10 @@
         <v>36</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>1022</v>
+        <v>1006</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>1041</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
@@ -9841,10 +9581,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>1059</v>
+        <v>1043</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>1071</v>
+        <v>1055</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>49</v>
@@ -9853,10 +9593,10 @@
         <v>62</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>1072</v>
+        <v>1056</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>1021</v>
+        <v>1005</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>88</v>
@@ -9865,10 +9605,10 @@
         <v>36</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>1022</v>
+        <v>1006</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>1041</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
@@ -9876,10 +9616,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>1059</v>
+        <v>1043</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>1073</v>
+        <v>1057</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>49</v>
@@ -9888,13 +9628,13 @@
         <v>62</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>1074</v>
+        <v>1058</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>1062</v>
+        <v>1046</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>890</v>
+        <v>874</v>
       </c>
       <c r="I19" s="1" t="s">
         <v>88</v>
@@ -9903,7 +9643,7 @@
         <v>88</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>1075</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
@@ -9911,10 +9651,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>1059</v>
+        <v>1043</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>1076</v>
+        <v>1060</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>49</v>
@@ -9923,22 +9663,22 @@
         <v>62</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>1077</v>
+        <v>1061</v>
       </c>
       <c r="G20" s="1" t="s">
+        <v>1046</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>874</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="K20" s="1" t="s">
         <v>1062</v>
-      </c>
-      <c r="H20" s="1" t="s">
-        <v>890</v>
-      </c>
-      <c r="I20" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="J20" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="K20" s="1" t="s">
-        <v>1078</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
@@ -9946,10 +9686,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>1059</v>
+        <v>1043</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>1079</v>
+        <v>1063</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>49</v>
@@ -9958,10 +9698,10 @@
         <v>62</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>1080</v>
+        <v>1064</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>1021</v>
+        <v>1005</v>
       </c>
       <c r="H21" s="1" t="s">
         <v>88</v>
@@ -9970,10 +9710,10 @@
         <v>36</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>1022</v>
+        <v>1006</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>1041</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
@@ -9981,10 +9721,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>1059</v>
+        <v>1043</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>1081</v>
+        <v>1065</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>49</v>
@@ -9993,10 +9733,10 @@
         <v>62</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>1082</v>
+        <v>1066</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>1021</v>
+        <v>1005</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>88</v>
@@ -10005,7 +9745,7 @@
         <v>0</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>1083</v>
+        <v>1067</v>
       </c>
       <c r="K22" s="1" t="s">
         <v>88</v>
@@ -10016,10 +9756,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>1059</v>
+        <v>1043</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>1084</v>
+        <v>1068</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>49</v>
@@ -10028,13 +9768,13 @@
         <v>71</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>1085</v>
+        <v>1069</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>1062</v>
+        <v>1046</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>890</v>
+        <v>874</v>
       </c>
       <c r="I23" s="1" t="s">
         <v>88</v>
@@ -10043,7 +9783,7 @@
         <v>88</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>1086</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
@@ -10051,10 +9791,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>1059</v>
+        <v>1043</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>1087</v>
+        <v>1071</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>49</v>
@@ -10063,10 +9803,10 @@
         <v>71</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>1088</v>
+        <v>1072</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>1021</v>
+        <v>1005</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>88</v>
@@ -10075,10 +9815,10 @@
         <v>1</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>1089</v>
+        <v>1073</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>1090</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
@@ -10086,10 +9826,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>1059</v>
+        <v>1043</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>1091</v>
+        <v>1075</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>49</v>
@@ -10098,10 +9838,10 @@
         <v>71</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>1092</v>
+        <v>1076</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>1021</v>
+        <v>1005</v>
       </c>
       <c r="H25" s="1" t="s">
         <v>88</v>
@@ -10110,10 +9850,10 @@
         <v>1</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>1093</v>
+        <v>1077</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>1094</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
@@ -10121,10 +9861,10 @@
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>1059</v>
+        <v>1043</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>1095</v>
+        <v>1079</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>49</v>
@@ -10133,10 +9873,10 @@
         <v>71</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>1096</v>
+        <v>1080</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>1021</v>
+        <v>1005</v>
       </c>
       <c r="H26" s="1" t="s">
         <v>88</v>
@@ -10145,10 +9885,10 @@
         <v>1</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>1089</v>
+        <v>1073</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>1090</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
@@ -10156,10 +9896,10 @@
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>1059</v>
+        <v>1043</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>1097</v>
+        <v>1081</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>49</v>
@@ -10168,13 +9908,13 @@
         <v>71</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>1098</v>
+        <v>1082</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>1062</v>
+        <v>1046</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>890</v>
+        <v>874</v>
       </c>
       <c r="I27" s="1" t="s">
         <v>88</v>
@@ -10183,7 +9923,7 @@
         <v>88</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>1099</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
@@ -10191,10 +9931,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>1059</v>
+        <v>1043</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>1100</v>
+        <v>1084</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>49</v>
@@ -10203,10 +9943,10 @@
         <v>71</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>1101</v>
+        <v>1085</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>1021</v>
+        <v>1005</v>
       </c>
       <c r="H28" s="1" t="s">
         <v>88</v>
@@ -10215,10 +9955,10 @@
         <v>1</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>1089</v>
+        <v>1073</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>1102</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
@@ -10226,10 +9966,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>1059</v>
+        <v>1043</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>1103</v>
+        <v>1087</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>49</v>
@@ -10238,10 +9978,10 @@
         <v>71</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>1104</v>
+        <v>1088</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>1021</v>
+        <v>1005</v>
       </c>
       <c r="H29" s="1" t="s">
         <v>88</v>
@@ -10250,10 +9990,10 @@
         <v>1</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>1089</v>
+        <v>1073</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>1090</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
@@ -10261,10 +10001,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>1059</v>
+        <v>1043</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>1105</v>
+        <v>1089</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>49</v>
@@ -10273,10 +10013,10 @@
         <v>71</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>1106</v>
+        <v>1090</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>1021</v>
+        <v>1005</v>
       </c>
       <c r="H30" s="1" t="s">
         <v>88</v>
@@ -10285,10 +10025,10 @@
         <v>1</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>1089</v>
+        <v>1073</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>1107</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
@@ -10296,10 +10036,10 @@
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>1059</v>
+        <v>1043</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>1108</v>
+        <v>1092</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>49</v>
@@ -10308,10 +10048,10 @@
         <v>50</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>1109</v>
+        <v>1093</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>1021</v>
+        <v>1005</v>
       </c>
       <c r="H31" s="1" t="s">
         <v>88</v>
@@ -10320,10 +10060,10 @@
         <v>240</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>1022</v>
+        <v>1006</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>1023</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
@@ -10331,10 +10071,10 @@
         <v>31</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>1059</v>
+        <v>1043</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>1110</v>
+        <v>1094</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>49</v>
@@ -10343,10 +10083,10 @@
         <v>62</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>1111</v>
+        <v>1095</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>1021</v>
+        <v>1005</v>
       </c>
       <c r="H32" s="1" t="s">
         <v>88</v>
@@ -10355,7 +10095,7 @@
         <v>0</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>1083</v>
+        <v>1067</v>
       </c>
       <c r="K32" s="1" t="s">
         <v>88</v>
@@ -10366,10 +10106,10 @@
         <v>32</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>1112</v>
+        <v>1096</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>1113</v>
+        <v>1097</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>49</v>
@@ -10378,13 +10118,13 @@
         <v>71</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>1106</v>
+        <v>1090</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>1062</v>
+        <v>1046</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>878</v>
+        <v>862</v>
       </c>
       <c r="I33" s="1" t="s">
         <v>88</v>
@@ -10393,7 +10133,7 @@
         <v>88</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>1114</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
@@ -10401,10 +10141,10 @@
         <v>33</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>1112</v>
+        <v>1096</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>1115</v>
+        <v>1099</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>49</v>
@@ -10413,10 +10153,10 @@
         <v>71</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>1116</v>
+        <v>1100</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>1021</v>
+        <v>1005</v>
       </c>
       <c r="H34" s="1" t="s">
         <v>88</v>
@@ -10425,10 +10165,10 @@
         <v>1</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>1089</v>
+        <v>1073</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>1117</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
@@ -10436,10 +10176,10 @@
         <v>34</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>1112</v>
+        <v>1096</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>1118</v>
+        <v>1102</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>49</v>
@@ -10448,13 +10188,13 @@
         <v>71</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>1119</v>
+        <v>1103</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>1062</v>
+        <v>1046</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>878</v>
+        <v>862</v>
       </c>
       <c r="I35" s="1" t="s">
         <v>88</v>
@@ -10463,7 +10203,7 @@
         <v>88</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>1120</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
@@ -10471,10 +10211,10 @@
         <v>35</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>1112</v>
+        <v>1096</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>1121</v>
+        <v>1105</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>49</v>
@@ -10483,13 +10223,13 @@
         <v>71</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>1122</v>
+        <v>1106</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>1062</v>
+        <v>1046</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>878</v>
+        <v>862</v>
       </c>
       <c r="I36" s="1" t="s">
         <v>88</v>
@@ -10498,7 +10238,7 @@
         <v>88</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>1123</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
@@ -10506,10 +10246,10 @@
         <v>36</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>1112</v>
+        <v>1096</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>1124</v>
+        <v>1108</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>49</v>
@@ -10518,10 +10258,10 @@
         <v>71</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>1125</v>
+        <v>1109</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>1021</v>
+        <v>1005</v>
       </c>
       <c r="H37" s="1" t="s">
         <v>88</v>
@@ -10530,10 +10270,10 @@
         <v>1</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>1089</v>
+        <v>1073</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>1107</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
@@ -10541,10 +10281,10 @@
         <v>37</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>1112</v>
+        <v>1096</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>1126</v>
+        <v>1110</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>49</v>
@@ -10553,10 +10293,10 @@
         <v>62</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>1127</v>
+        <v>1111</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>1021</v>
+        <v>1005</v>
       </c>
       <c r="H38" s="1" t="s">
         <v>88</v>
@@ -10565,10 +10305,10 @@
         <v>36</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>1022</v>
+        <v>1006</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>1041</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
@@ -10576,10 +10316,10 @@
         <v>38</v>
       </c>
       <c r="B39" s="1" t="s">
+        <v>1096</v>
+      </c>
+      <c r="C39" s="1" t="s">
         <v>1112</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>1128</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>49</v>
@@ -10588,10 +10328,10 @@
         <v>62</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>1129</v>
+        <v>1113</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>1021</v>
+        <v>1005</v>
       </c>
       <c r="H39" s="1" t="s">
         <v>88</v>
@@ -10600,10 +10340,10 @@
         <v>36</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>1022</v>
+        <v>1006</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>1041</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
@@ -10611,10 +10351,10 @@
         <v>39</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>1112</v>
+        <v>1096</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>1130</v>
+        <v>1114</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>49</v>
@@ -10623,10 +10363,10 @@
         <v>62</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>1131</v>
+        <v>1115</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>1021</v>
+        <v>1005</v>
       </c>
       <c r="H40" s="1" t="s">
         <v>88</v>
@@ -10635,7 +10375,7 @@
         <v>0</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>1083</v>
+        <v>1067</v>
       </c>
       <c r="K40" s="1" t="s">
         <v>88</v>
@@ -10666,22 +10406,22 @@
         <v>40</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>1132</v>
+        <v>1116</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>1059</v>
+        <v>1043</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>1133</v>
+        <v>1117</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>1134</v>
+        <v>1118</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>1135</v>
+        <v>1119</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>1136</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -10689,22 +10429,22 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>1137</v>
+        <v>1121</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>1138</v>
+        <v>1122</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>1139</v>
+        <v>1123</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>1140</v>
+        <v>1124</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>1141</v>
+        <v>1125</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>1142</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -10712,22 +10452,22 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1137</v>
+        <v>1121</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>1143</v>
+        <v>1127</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>1144</v>
+        <v>1128</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>1145</v>
+        <v>1129</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>1146</v>
+        <v>1130</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>1147</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -10735,22 +10475,22 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>1137</v>
+        <v>1121</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>1148</v>
+        <v>1132</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>1144</v>
+        <v>1128</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>1149</v>
+        <v>1133</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>1150</v>
+        <v>1134</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>1151</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -10758,22 +10498,22 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>1152</v>
+        <v>1136</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>1153</v>
+        <v>1137</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>1154</v>
+        <v>1138</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>1155</v>
+        <v>1139</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>1156</v>
+        <v>1140</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>1157</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -10781,22 +10521,22 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>1152</v>
+        <v>1136</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>1158</v>
+        <v>1142</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>1159</v>
+        <v>1143</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>1160</v>
+        <v>1144</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>1161</v>
+        <v>1145</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>1162</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -10804,22 +10544,22 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>1163</v>
+        <v>1147</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>1164</v>
+        <v>1148</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>1005</v>
+        <v>989</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>1165</v>
+        <v>1149</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>1166</v>
+        <v>1150</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>1167</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -10827,22 +10567,22 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>1163</v>
+        <v>1147</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>1168</v>
+        <v>1152</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>988</v>
+        <v>972</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>1169</v>
+        <v>1153</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>1170</v>
+        <v>1154</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>1171</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -10850,22 +10590,22 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>1163</v>
+        <v>1147</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>1172</v>
+        <v>1156</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>845</v>
+        <v>831</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>1173</v>
+        <v>1157</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>1174</v>
+        <v>1158</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>1175</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -10873,22 +10613,22 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
+        <v>1147</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>1160</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>989</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>1161</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>1162</v>
+      </c>
+      <c r="G10" s="1" t="s">
         <v>1163</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>1176</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>1005</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>1177</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>1178</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>1179</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -10896,22 +10636,22 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>1180</v>
+        <v>1164</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>1181</v>
+        <v>1165</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>1154</v>
+        <v>1138</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>1182</v>
+        <v>1166</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>1183</v>
+        <v>1167</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>1184</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -10919,22 +10659,22 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>1180</v>
+        <v>1164</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>1185</v>
+        <v>1169</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>975</v>
+        <v>959</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>1186</v>
+        <v>1170</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>1187</v>
+        <v>1171</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>1188</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -10942,22 +10682,22 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>1137</v>
+        <v>1121</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>1189</v>
+        <v>1173</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>1144</v>
+        <v>1128</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>1190</v>
+        <v>1174</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>1191</v>
+        <v>1175</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>1192</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -10965,22 +10705,22 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>1152</v>
+        <v>1136</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>1193</v>
+        <v>1177</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>1144</v>
+        <v>1128</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>1194</v>
+        <v>1178</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>1195</v>
+        <v>1179</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>1196</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -10988,22 +10728,22 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>1180</v>
+        <v>1164</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>1197</v>
+        <v>1181</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>1144</v>
+        <v>1128</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>1198</v>
+        <v>1182</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>1199</v>
+        <v>1183</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>1200</v>
+        <v>1184</v>
       </c>
     </row>
   </sheetData>
@@ -11026,125 +10766,125 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>1201</v>
+        <v>1185</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>1202</v>
+        <v>1186</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>1203</v>
+        <v>1187</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>942</v>
+        <v>926</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>1204</v>
+        <v>1188</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>1205</v>
+        <v>1189</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>1206</v>
+        <v>1190</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>1207</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>1204</v>
+        <v>1188</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1208</v>
+        <v>1192</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>1209</v>
+        <v>1193</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>1210</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>1204</v>
+        <v>1188</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>1211</v>
+        <v>1195</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>1209</v>
+        <v>1193</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>1212</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>1204</v>
+        <v>1188</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>1213</v>
+        <v>1197</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>1209</v>
+        <v>1193</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>1214</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>1204</v>
+        <v>1188</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>1215</v>
+        <v>1199</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>1209</v>
+        <v>1193</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>1214</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>1204</v>
+        <v>1188</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>1216</v>
+        <v>1200</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>1217</v>
+        <v>1201</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>1218</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>1188</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>1203</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>1193</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>1204</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>1219</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>1209</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>1220</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>1221</v>
+        <v>1205</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>1222</v>
+        <v>1206</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>1223</v>
+        <v>1207</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>88</v>
@@ -11152,184 +10892,184 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>1221</v>
+        <v>1205</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>1224</v>
+        <v>1208</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>1225</v>
+        <v>1209</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>1226</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>1221</v>
+        <v>1205</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>1227</v>
+        <v>1211</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>1228</v>
+        <v>1212</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>1229</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>1221</v>
+        <v>1205</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>1230</v>
+        <v>1214</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>1231</v>
+        <v>1215</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>1232</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>1233</v>
+        <v>1217</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>1234</v>
+        <v>1218</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>1235</v>
+        <v>1219</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>1236</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>1233</v>
+        <v>1217</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>1237</v>
+        <v>1221</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>1238</v>
+        <v>1222</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>1239</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>1240</v>
+        <v>1224</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>1241</v>
+        <v>1225</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>1242</v>
+        <v>1226</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>1243</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>1244</v>
+        <v>1228</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>1245</v>
+        <v>1229</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>1246</v>
+        <v>1230</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>1247</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>1244</v>
+        <v>1228</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>1248</v>
+        <v>1232</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>1249</v>
+        <v>1233</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>1250</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>1244</v>
+        <v>1228</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>1251</v>
+        <v>1235</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>1252</v>
+        <v>1236</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>1253</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>1244</v>
+        <v>1228</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>1254</v>
+        <v>1238</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>1255</v>
+        <v>1239</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>1256</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>1257</v>
+        <v>1241</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>1258</v>
+        <v>1242</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>1259</v>
+        <v>1243</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>1260</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>1257</v>
+        <v>1241</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>1261</v>
+        <v>1245</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>1262</v>
+        <v>1246</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>1263</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>1264</v>
+        <v>1248</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>1265</v>
+        <v>1249</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>1266</v>
+        <v>1250</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>1267</v>
+        <v>1251</v>
       </c>
     </row>
   </sheetData>
@@ -11672,31 +11412,31 @@
         <v>40</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>1010</v>
+        <v>994</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>1011</v>
+        <v>995</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>42</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>1012</v>
+        <v>996</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>1013</v>
+        <v>997</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>1014</v>
+        <v>998</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>1015</v>
+        <v>999</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>1268</v>
+        <v>1252</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>1269</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -11704,19 +11444,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>1270</v>
+        <v>1254</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>1271</v>
+        <v>1255</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>50</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>1061</v>
+        <v>1045</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>1021</v>
+        <v>1005</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>88</v>
@@ -11728,7 +11468,7 @@
         <v>175</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>1272</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -11736,19 +11476,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1270</v>
+        <v>1254</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>1273</v>
+        <v>1257</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>50</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>1274</v>
+        <v>1258</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>1021</v>
+        <v>1005</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>88</v>
@@ -11760,7 +11500,7 @@
         <v>175</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>1272</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -11768,19 +11508,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>1270</v>
+        <v>1254</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>1275</v>
+        <v>1259</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>50</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>1276</v>
+        <v>1260</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>1021</v>
+        <v>1005</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>88</v>
@@ -11792,7 +11532,7 @@
         <v>175</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>1272</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -11800,22 +11540,22 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>1270</v>
+        <v>1254</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>1277</v>
+        <v>1261</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>50</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>1278</v>
+        <v>1262</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>1062</v>
+        <v>1046</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>870</v>
+        <v>856</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>88</v>
@@ -11832,19 +11572,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>1270</v>
+        <v>1254</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>1279</v>
+        <v>1263</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>50</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>1280</v>
+        <v>1264</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>1021</v>
+        <v>1005</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>88</v>
@@ -11856,7 +11596,7 @@
         <v>175</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>1272</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -11864,19 +11604,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>1281</v>
+        <v>1265</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>1282</v>
+        <v>1266</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>50</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>1020</v>
+        <v>1004</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>1021</v>
+        <v>1005</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>88</v>
@@ -11888,7 +11628,7 @@
         <v>175</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>1272</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -11896,7 +11636,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>1281</v>
+        <v>1265</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>669</v>
@@ -11908,7 +11648,7 @@
         <v>273</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>1021</v>
+        <v>1005</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>88</v>
@@ -11920,7 +11660,7 @@
         <v>175</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>1272</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -11928,19 +11668,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>1281</v>
+        <v>1265</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>1283</v>
+        <v>1267</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>50</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>1284</v>
+        <v>1268</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>1021</v>
+        <v>1005</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>88</v>
@@ -11952,7 +11692,7 @@
         <v>175</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>1272</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -11960,19 +11700,19 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>1281</v>
+        <v>1265</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>1285</v>
+        <v>1269</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>50</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>1286</v>
+        <v>1270</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>1021</v>
+        <v>1005</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>88</v>
@@ -11984,7 +11724,7 @@
         <v>175</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>1272</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
@@ -11992,19 +11732,19 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>1281</v>
+        <v>1265</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>1287</v>
+        <v>1271</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>50</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>1288</v>
+        <v>1272</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>1021</v>
+        <v>1005</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>88</v>
@@ -12016,7 +11756,7 @@
         <v>175</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>1272</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
@@ -12024,22 +11764,22 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>1281</v>
+        <v>1265</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>1289</v>
+        <v>1273</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>50</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>1290</v>
+        <v>1274</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>1062</v>
+        <v>1046</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>904</v>
+        <v>888</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>88</v>
@@ -12056,19 +11796,19 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>1281</v>
+        <v>1265</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>1291</v>
+        <v>1275</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>50</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>1292</v>
+        <v>1276</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>1021</v>
+        <v>1005</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>88</v>
@@ -12080,7 +11820,7 @@
         <v>175</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>1272</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
@@ -12088,19 +11828,19 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>1281</v>
+        <v>1265</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>1293</v>
+        <v>1277</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>50</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>1294</v>
+        <v>1278</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>1021</v>
+        <v>1005</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>88</v>
@@ -12112,7 +11852,7 @@
         <v>175</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>1272</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
@@ -12120,22 +11860,22 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>1281</v>
+        <v>1265</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>1295</v>
+        <v>1279</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>50</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>1296</v>
+        <v>1280</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>1062</v>
+        <v>1046</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>870</v>
+        <v>856</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>88</v>
@@ -12152,22 +11892,22 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
+        <v>1265</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>1281</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>1297</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>50</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>1298</v>
+        <v>1282</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>1062</v>
+        <v>1046</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>898</v>
+        <v>882</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>88</v>
@@ -12184,10 +11924,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>1299</v>
+        <v>1283</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>1300</v>
+        <v>1284</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>50</v>
@@ -12196,7 +11936,7 @@
         <v>273</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>1021</v>
+        <v>1005</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>88</v>
@@ -12208,7 +11948,7 @@
         <v>175</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>1272</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
@@ -12216,19 +11956,19 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>1299</v>
+        <v>1283</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>1301</v>
+        <v>1285</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>50</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>1302</v>
+        <v>1286</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>1021</v>
+        <v>1005</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>88</v>
@@ -12248,19 +11988,19 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>1299</v>
+        <v>1283</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>1248</v>
+        <v>1232</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>50</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>1303</v>
+        <v>1287</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>1021</v>
+        <v>1005</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>88</v>
@@ -12269,10 +12009,10 @@
         <v>720</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>1304</v>
+        <v>1288</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>1272</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
@@ -12280,19 +12020,19 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>1299</v>
+        <v>1283</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>1305</v>
+        <v>1289</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>50</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>1025</v>
+        <v>1009</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>1021</v>
+        <v>1005</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>88</v>
@@ -12301,10 +12041,10 @@
         <v>480</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>1306</v>
+        <v>1290</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>1272</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
@@ -12312,19 +12052,19 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>1299</v>
+        <v>1283</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>1307</v>
+        <v>1291</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>50</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>1308</v>
+        <v>1292</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>1021</v>
+        <v>1005</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>88</v>
@@ -12333,10 +12073,10 @@
         <v>720</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>1304</v>
+        <v>1288</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>1272</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
@@ -12344,19 +12084,19 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>1299</v>
+        <v>1283</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>1309</v>
+        <v>1293</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>50</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>1109</v>
+        <v>1093</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>1021</v>
+        <v>1005</v>
       </c>
       <c r="G22" s="1" t="s">
         <v>88</v>
@@ -12368,7 +12108,7 @@
         <v>175</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>1272</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
@@ -12376,19 +12116,19 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>1299</v>
+        <v>1283</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>1261</v>
+        <v>1245</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>50</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>1310</v>
+        <v>1294</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>1021</v>
+        <v>1005</v>
       </c>
       <c r="G23" s="1" t="s">
         <v>88</v>
@@ -12408,19 +12148,19 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>1299</v>
+        <v>1283</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>1311</v>
+        <v>1295</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>50</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>1312</v>
+        <v>1296</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>1021</v>
+        <v>1005</v>
       </c>
       <c r="G24" s="1" t="s">
         <v>88</v>
@@ -12429,10 +12169,10 @@
         <v>31335</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>1313</v>
+        <v>1297</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>1272</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
@@ -12440,19 +12180,19 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>1314</v>
+        <v>1298</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>1315</v>
+        <v>1299</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>58</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>1316</v>
+        <v>1300</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>1021</v>
+        <v>1005</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>88</v>
@@ -12464,7 +12204,7 @@
         <v>175</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>1272</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
@@ -12472,19 +12212,19 @@
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>1314</v>
+        <v>1298</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>1317</v>
+        <v>1301</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>58</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>1318</v>
+        <v>1302</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>1021</v>
+        <v>1005</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>88</v>
@@ -12496,7 +12236,7 @@
         <v>175</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>1272</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
@@ -12504,19 +12244,19 @@
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>1314</v>
+        <v>1298</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>1319</v>
+        <v>1303</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>61</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>1320</v>
+        <v>1304</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>1021</v>
+        <v>1005</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>88</v>
@@ -12528,7 +12268,7 @@
         <v>175</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>1272</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
@@ -12536,19 +12276,19 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>1314</v>
+        <v>1298</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>1321</v>
+        <v>1305</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>61</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>1322</v>
+        <v>1306</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>1021</v>
+        <v>1005</v>
       </c>
       <c r="G28" s="1" t="s">
         <v>88</v>
@@ -12560,7 +12300,7 @@
         <v>175</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>1272</v>
+        <v>1256</v>
       </c>
     </row>
   </sheetData>
@@ -12583,24 +12323,24 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>1012</v>
+        <v>996</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>1323</v>
+        <v>1307</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>1324</v>
+        <v>1308</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>1325</v>
+        <v>1309</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>1326</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>1327</v>
+        <v>1311</v>
       </c>
       <c r="B2" s="1">
         <v>10</v>
@@ -12612,12 +12352,12 @@
         <v>0</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>1328</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>1329</v>
+        <v>1313</v>
       </c>
       <c r="B3" s="1">
         <v>15</v>
@@ -12629,12 +12369,12 @@
         <v>1</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>1330</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>1331</v>
+        <v>1315</v>
       </c>
       <c r="B4" s="1">
         <v>15</v>
@@ -12646,12 +12386,12 @@
         <v>0</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>1332</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>1333</v>
+        <v>1317</v>
       </c>
       <c r="B5" s="1">
         <v>3</v>
@@ -12663,12 +12403,12 @@
         <v>3</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>1334</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>1335</v>
+        <v>1319</v>
       </c>
       <c r="B6" s="1">
         <v>3</v>
@@ -12680,12 +12420,12 @@
         <v>3</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>1334</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>1336</v>
+        <v>1320</v>
       </c>
       <c r="B7" s="1">
         <v>3</v>
@@ -12697,12 +12437,12 @@
         <v>3</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>1334</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>1337</v>
+        <v>1321</v>
       </c>
       <c r="B8" s="1">
         <v>3</v>
@@ -12714,12 +12454,12 @@
         <v>3</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>1338</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>1339</v>
+        <v>1323</v>
       </c>
       <c r="B9" s="1">
         <v>8</v>
@@ -12731,7 +12471,7 @@
         <v>4</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>1340</v>
+        <v>1324</v>
       </c>
     </row>
   </sheetData>
